--- a/result.xlsx
+++ b/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,30 +429,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>DEEP LEARNINg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>deep learning</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>machine learning</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>training data</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>schreibtisch</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
@@ -464,29 +454,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1912.09789v1.pdf</t>
+          <t>test_A.pdf</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -495,29 +479,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1908.00080v4.pdf</t>
+          <t>test_hyphenation.pdf</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>868</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -526,29 +504,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2108.00941v3.pdf</t>
+          <t>test_B.pdf</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>409</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -557,29 +529,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2308.11254v1.pdf</t>
+          <t>test_C.pdf</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>298</v>
       </c>
     </row>
     <row r="6">
@@ -588,29 +554,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2402.06196v3.pdf</t>
+          <t>image_pdf.pdf</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>179</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>chinese.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
